--- a/DataTables/Datas/#VSPassive.xlsx
+++ b/DataTables/Datas/#VSPassive.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,6 +680,44 @@
         <v>5</v>
       </c>
     </row>
+    <row r="12">
+      <c r="B12" t="n">
+        <v>9</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>范围扩大</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>5</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="F12" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="n">
+        <v>10</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>弹速提升</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>7</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F13" t="n">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
